--- a/data_lake/datos_diarios_preliminares/dt=2026-09-04/Temp-max-septiembre-26.xlsx
+++ b/data_lake/datos_diarios_preliminares/dt=2026-09-04/Temp-max-septiembre-26.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.187.8\Oficina\Mi unidad\OSPA\02. Datos Diarios\Tablas\Datos hidrometeorologicos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\02. Datos Diarios\Tablas\Datos hidrometeorologicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{294F0F37-06B9-406C-9083-3F06445BC7CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9707DFD-C98D-4D16-931B-72D3EFB4CB20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9431,7 +9431,9 @@
       <c r="F5" s="63">
         <v>32.4</v>
       </c>
-      <c r="G5" s="63"/>
+      <c r="G5" s="63">
+        <v>32.1</v>
+      </c>
       <c r="H5" s="63"/>
       <c r="I5" s="63"/>
       <c r="J5" s="63"/>
@@ -9462,7 +9464,7 @@
       <c r="AI5" s="63"/>
       <c r="AJ5" s="36">
         <f>+IF(SUM($E5:$AI5)&gt;0,LOOKUP(1000,$E5:$AI5),NA())</f>
-        <v>32.4</v>
+        <v>32.1</v>
       </c>
       <c r="AK5" s="21">
         <f>+MAX($E5:$AI5)</f>
@@ -9507,7 +9509,9 @@
       <c r="F6" s="63">
         <v>32.1</v>
       </c>
-      <c r="G6" s="63"/>
+      <c r="G6" s="63">
+        <v>32.200000000000003</v>
+      </c>
       <c r="H6" s="63"/>
       <c r="I6" s="63"/>
       <c r="J6" s="63"/>
@@ -9538,18 +9542,18 @@
       <c r="AI6" s="63"/>
       <c r="AJ6" s="36">
         <f t="shared" ref="AJ6:AJ48" si="0">+IF(SUM($E6:$AI6)&gt;0,LOOKUP(1000,$E6:$AI6),NA())</f>
-        <v>32.1</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="AK6" s="21">
         <f t="shared" ref="AK6:AK48" si="1">+MAX($E6:$AI6)</f>
-        <v>32.1</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="AL6" s="22">
         <v>33.200000000000003</v>
       </c>
       <c r="AM6" s="23">
         <f t="shared" ref="AM6:AM48" si="2">IF(AK6&gt;0,$AK6-$AL6,"")</f>
-        <v>-1.1000000000000014</v>
+        <v>-1</v>
       </c>
       <c r="AN6" s="23">
         <v>31.213724845269681</v>
@@ -9583,7 +9587,9 @@
       <c r="F7" s="63">
         <v>34.799999999999997</v>
       </c>
-      <c r="G7" s="63"/>
+      <c r="G7" s="63">
+        <v>35.200000000000003</v>
+      </c>
       <c r="H7" s="63"/>
       <c r="I7" s="63"/>
       <c r="J7" s="63"/>
@@ -9614,18 +9620,18 @@
       <c r="AI7" s="63"/>
       <c r="AJ7" s="36">
         <f t="shared" si="0"/>
-        <v>34.799999999999997</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="AK7" s="21">
         <f t="shared" si="1"/>
-        <v>34.799999999999997</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="AL7" s="22">
         <v>37.200000000000003</v>
       </c>
       <c r="AM7" s="23">
         <f t="shared" si="2"/>
-        <v>-2.4000000000000057</v>
+        <v>-2</v>
       </c>
       <c r="AN7" s="23">
         <v>32.888880131362889</v>
@@ -9659,7 +9665,9 @@
       <c r="F8" s="63">
         <v>33.9</v>
       </c>
-      <c r="G8" s="63"/>
+      <c r="G8" s="63">
+        <v>33.700000000000003</v>
+      </c>
       <c r="H8" s="63"/>
       <c r="I8" s="63"/>
       <c r="J8" s="63"/>
@@ -9690,7 +9698,7 @@
       <c r="AI8" s="63"/>
       <c r="AJ8" s="36">
         <f t="shared" si="0"/>
-        <v>33.9</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="AK8" s="21">
         <f t="shared" si="1"/>
@@ -9735,7 +9743,9 @@
       <c r="F9" s="63">
         <v>35.6</v>
       </c>
-      <c r="G9" s="63"/>
+      <c r="G9" s="63">
+        <v>36.700000000000003</v>
+      </c>
       <c r="H9" s="63"/>
       <c r="I9" s="63"/>
       <c r="J9" s="63"/>
@@ -9766,18 +9776,18 @@
       <c r="AI9" s="63"/>
       <c r="AJ9" s="36">
         <f t="shared" si="0"/>
-        <v>35.6</v>
+        <v>36.700000000000003</v>
       </c>
       <c r="AK9" s="21">
         <f t="shared" si="1"/>
-        <v>35.6</v>
+        <v>36.700000000000003</v>
       </c>
       <c r="AL9" s="22">
         <v>38.4</v>
       </c>
       <c r="AM9" s="23">
         <f t="shared" si="2"/>
-        <v>-2.7999999999999972</v>
+        <v>-1.6999999999999957</v>
       </c>
       <c r="AN9" s="23">
         <v>33.308997701149423</v>
@@ -9811,7 +9821,9 @@
       <c r="F10" s="63">
         <v>34.299999999999997</v>
       </c>
-      <c r="G10" s="63"/>
+      <c r="G10" s="63">
+        <v>37.4</v>
+      </c>
       <c r="H10" s="63"/>
       <c r="I10" s="63"/>
       <c r="J10" s="63"/>
@@ -9842,18 +9854,18 @@
       <c r="AI10" s="63"/>
       <c r="AJ10" s="36">
         <f t="shared" si="0"/>
-        <v>34.299999999999997</v>
+        <v>37.4</v>
       </c>
       <c r="AK10" s="21">
         <f t="shared" si="1"/>
-        <v>34.700000000000003</v>
+        <v>37.4</v>
       </c>
       <c r="AL10" s="22">
         <v>39.6</v>
       </c>
       <c r="AM10" s="23">
         <f t="shared" si="2"/>
-        <v>-4.8999999999999986</v>
+        <v>-2.2000000000000028</v>
       </c>
       <c r="AN10" s="23">
         <v>33.75991221422256</v>
@@ -9887,7 +9899,9 @@
       <c r="F11" s="63">
         <v>37</v>
       </c>
-      <c r="G11" s="63"/>
+      <c r="G11" s="63">
+        <v>37.799999999999997</v>
+      </c>
       <c r="H11" s="63"/>
       <c r="I11" s="63"/>
       <c r="J11" s="63"/>
@@ -9918,18 +9932,18 @@
       <c r="AI11" s="63"/>
       <c r="AJ11" s="36">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="AK11" s="21">
         <f t="shared" si="1"/>
-        <v>37</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="AL11" s="22">
         <v>40.200000000000003</v>
       </c>
       <c r="AM11" s="23">
         <f t="shared" si="2"/>
-        <v>-3.2000000000000028</v>
+        <v>-2.4000000000000057</v>
       </c>
       <c r="AN11" s="23">
         <v>34.012164961475307</v>
@@ -9963,7 +9977,9 @@
       <c r="F12" s="63">
         <v>33.200000000000003</v>
       </c>
-      <c r="G12" s="63"/>
+      <c r="G12" s="63">
+        <v>34.200000000000003</v>
+      </c>
       <c r="H12" s="63"/>
       <c r="I12" s="63"/>
       <c r="J12" s="63"/>
@@ -9994,18 +10010,18 @@
       <c r="AI12" s="63"/>
       <c r="AJ12" s="36">
         <f t="shared" si="0"/>
-        <v>33.200000000000003</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="AK12" s="21">
         <f t="shared" si="1"/>
-        <v>34</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="AL12" s="22">
         <v>36</v>
       </c>
       <c r="AM12" s="23">
         <f t="shared" si="2"/>
-        <v>-2</v>
+        <v>-1.7999999999999972</v>
       </c>
       <c r="AN12" s="23">
         <v>31.452593153972469</v>
@@ -10039,7 +10055,9 @@
       <c r="F13" s="63">
         <v>34.6</v>
       </c>
-      <c r="G13" s="63"/>
+      <c r="G13" s="63">
+        <v>34.799999999999997</v>
+      </c>
       <c r="H13" s="63"/>
       <c r="I13" s="63"/>
       <c r="J13" s="63"/>
@@ -10070,18 +10088,18 @@
       <c r="AI13" s="63"/>
       <c r="AJ13" s="36">
         <f t="shared" si="0"/>
-        <v>34.6</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="AK13" s="21">
         <f t="shared" si="1"/>
-        <v>34.6</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="AL13" s="22">
         <v>37.4</v>
       </c>
       <c r="AM13" s="23">
         <f t="shared" si="2"/>
-        <v>-2.7999999999999972</v>
+        <v>-2.6000000000000014</v>
       </c>
       <c r="AN13" s="23">
         <v>32.199781609195398</v>
@@ -10115,7 +10133,9 @@
       <c r="F14" s="63">
         <v>34.1</v>
       </c>
-      <c r="G14" s="63"/>
+      <c r="G14" s="63">
+        <v>36.1</v>
+      </c>
       <c r="H14" s="63"/>
       <c r="I14" s="63"/>
       <c r="J14" s="63"/>
@@ -10146,18 +10166,18 @@
       <c r="AI14" s="63"/>
       <c r="AJ14" s="36">
         <f t="shared" si="0"/>
-        <v>34.1</v>
+        <v>36.1</v>
       </c>
       <c r="AK14" s="21">
         <f t="shared" si="1"/>
-        <v>34.6</v>
+        <v>36.1</v>
       </c>
       <c r="AL14" s="22">
         <v>37.5</v>
       </c>
       <c r="AM14" s="23">
         <f t="shared" si="2"/>
-        <v>-2.8999999999999986</v>
+        <v>-1.3999999999999986</v>
       </c>
       <c r="AN14" s="23">
         <v>32.561237881007962</v>
@@ -10191,7 +10211,9 @@
       <c r="F15" s="63">
         <v>31.9</v>
       </c>
-      <c r="G15" s="63"/>
+      <c r="G15" s="63">
+        <v>31.8</v>
+      </c>
       <c r="H15" s="63"/>
       <c r="I15" s="63"/>
       <c r="J15" s="63"/>
@@ -10222,7 +10244,7 @@
       <c r="AI15" s="63"/>
       <c r="AJ15" s="36">
         <f t="shared" si="0"/>
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="AK15" s="21">
         <f t="shared" si="1"/>
@@ -10316,7 +10338,9 @@
       <c r="F17" s="63">
         <v>33.799999999999997</v>
       </c>
-      <c r="G17" s="63"/>
+      <c r="G17" s="63">
+        <v>35.4</v>
+      </c>
       <c r="H17" s="63"/>
       <c r="I17" s="63"/>
       <c r="J17" s="63"/>
@@ -10347,18 +10371,18 @@
       <c r="AI17" s="63"/>
       <c r="AJ17" s="36">
         <f t="shared" si="0"/>
-        <v>33.799999999999997</v>
+        <v>35.4</v>
       </c>
       <c r="AK17" s="21">
         <f t="shared" si="1"/>
-        <v>35</v>
+        <v>35.4</v>
       </c>
       <c r="AL17" s="22">
         <v>36.6</v>
       </c>
       <c r="AM17" s="23">
         <f t="shared" si="2"/>
-        <v>-1.6000000000000014</v>
+        <v>-1.2000000000000028</v>
       </c>
       <c r="AN17" s="23">
         <v>32.028002378121293</v>
@@ -10392,7 +10416,9 @@
       <c r="F18" s="63">
         <v>26.3</v>
       </c>
-      <c r="G18" s="63"/>
+      <c r="G18" s="63">
+        <v>29.2</v>
+      </c>
       <c r="H18" s="63"/>
       <c r="I18" s="63"/>
       <c r="J18" s="63"/>
@@ -10423,18 +10449,18 @@
       <c r="AI18" s="63"/>
       <c r="AJ18" s="36">
         <f t="shared" si="0"/>
-        <v>26.3</v>
+        <v>29.2</v>
       </c>
       <c r="AK18" s="21">
         <f t="shared" si="1"/>
-        <v>28.6</v>
+        <v>29.2</v>
       </c>
       <c r="AL18" s="22">
         <v>31.8</v>
       </c>
       <c r="AM18" s="23">
         <f t="shared" si="2"/>
-        <v>-3.1999999999999993</v>
+        <v>-2.6000000000000014</v>
       </c>
       <c r="AN18" s="23">
         <v>26.245613553113561</v>
@@ -10468,7 +10494,9 @@
       <c r="F19" s="63">
         <v>36.6</v>
       </c>
-      <c r="G19" s="63"/>
+      <c r="G19" s="63">
+        <v>37</v>
+      </c>
       <c r="H19" s="63"/>
       <c r="I19" s="63"/>
       <c r="J19" s="63"/>
@@ -10499,7 +10527,7 @@
       <c r="AI19" s="63"/>
       <c r="AJ19" s="36">
         <f t="shared" si="0"/>
-        <v>36.6</v>
+        <v>37</v>
       </c>
       <c r="AK19" s="21">
         <f t="shared" si="1"/>
@@ -10544,7 +10572,9 @@
       <c r="F20" s="63">
         <v>30.8</v>
       </c>
-      <c r="G20" s="63"/>
+      <c r="G20" s="63">
+        <v>31.9</v>
+      </c>
       <c r="H20" s="63"/>
       <c r="I20" s="63"/>
       <c r="J20" s="63"/>
@@ -10575,18 +10605,18 @@
       <c r="AI20" s="63"/>
       <c r="AJ20" s="36">
         <f t="shared" si="0"/>
-        <v>30.8</v>
+        <v>31.9</v>
       </c>
       <c r="AK20" s="21">
         <f t="shared" si="1"/>
-        <v>30.8</v>
+        <v>31.9</v>
       </c>
       <c r="AL20" s="22">
         <v>33.1</v>
       </c>
       <c r="AM20" s="23">
         <f t="shared" si="2"/>
-        <v>-2.3000000000000007</v>
+        <v>-1.2000000000000028</v>
       </c>
       <c r="AN20" s="23">
         <v>28.140217569786529</v>
@@ -10620,7 +10650,9 @@
       <c r="F21" s="63">
         <v>24</v>
       </c>
-      <c r="G21" s="63"/>
+      <c r="G21" s="63">
+        <v>24.8</v>
+      </c>
       <c r="H21" s="63"/>
       <c r="I21" s="63"/>
       <c r="J21" s="63"/>
@@ -10651,18 +10683,18 @@
       <c r="AI21" s="63"/>
       <c r="AJ21" s="36">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>24.8</v>
       </c>
       <c r="AK21" s="21">
         <f t="shared" si="1"/>
-        <v>24.2</v>
+        <v>24.8</v>
       </c>
       <c r="AL21" s="22">
         <v>26.9</v>
       </c>
       <c r="AM21" s="23">
         <f t="shared" si="2"/>
-        <v>-2.6999999999999993</v>
+        <v>-2.0999999999999979</v>
       </c>
       <c r="AN21" s="23">
         <v>22.564435196194999</v>
@@ -10762,7 +10794,9 @@
       <c r="F23" s="63">
         <v>28</v>
       </c>
-      <c r="G23" s="63"/>
+      <c r="G23" s="63">
+        <v>30.2</v>
+      </c>
       <c r="H23" s="63"/>
       <c r="I23" s="63"/>
       <c r="J23" s="63"/>
@@ -10793,18 +10827,18 @@
       <c r="AI23" s="63"/>
       <c r="AJ23" s="36">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>30.2</v>
       </c>
       <c r="AK23" s="21">
         <f t="shared" si="1"/>
-        <v>28</v>
+        <v>30.2</v>
       </c>
       <c r="AL23" s="22">
         <v>32.799999999999997</v>
       </c>
       <c r="AM23" s="23">
         <f t="shared" si="2"/>
-        <v>-4.7999999999999972</v>
+        <v>-2.5999999999999979</v>
       </c>
       <c r="AN23" s="23">
         <v>27.03996905393457</v>
@@ -10838,7 +10872,9 @@
       <c r="F24" s="63">
         <v>30.6</v>
       </c>
-      <c r="G24" s="63"/>
+      <c r="G24" s="63">
+        <v>32.200000000000003</v>
+      </c>
       <c r="H24" s="63"/>
       <c r="I24" s="63"/>
       <c r="J24" s="63"/>
@@ -10869,18 +10905,18 @@
       <c r="AI24" s="63"/>
       <c r="AJ24" s="36">
         <f t="shared" si="0"/>
-        <v>30.6</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="AK24" s="21">
         <f t="shared" si="1"/>
-        <v>30.6</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="AL24" s="22">
         <v>35</v>
       </c>
       <c r="AM24" s="23">
         <f t="shared" si="2"/>
-        <v>-4.3999999999999986</v>
+        <v>-2.7999999999999972</v>
       </c>
       <c r="AN24" s="23">
         <v>28.21960773581463</v>
@@ -10914,7 +10950,9 @@
       <c r="F25" s="63">
         <v>32.1</v>
       </c>
-      <c r="G25" s="63"/>
+      <c r="G25" s="63">
+        <v>33.4</v>
+      </c>
       <c r="H25" s="63"/>
       <c r="I25" s="63"/>
       <c r="J25" s="63"/>
@@ -10945,18 +10983,18 @@
       <c r="AI25" s="63"/>
       <c r="AJ25" s="36">
         <f t="shared" si="0"/>
-        <v>32.1</v>
+        <v>33.4</v>
       </c>
       <c r="AK25" s="21">
         <f t="shared" si="1"/>
-        <v>32.200000000000003</v>
+        <v>33.4</v>
       </c>
       <c r="AL25" s="22">
         <v>36.799999999999997</v>
       </c>
       <c r="AM25" s="23">
         <f t="shared" si="2"/>
-        <v>-4.5999999999999943</v>
+        <v>-3.3999999999999986</v>
       </c>
       <c r="AN25" s="23">
         <v>30.83648877941982</v>
@@ -10990,7 +11028,9 @@
       <c r="F26" s="63">
         <v>19.3</v>
       </c>
-      <c r="G26" s="63"/>
+      <c r="G26" s="63">
+        <v>18.5</v>
+      </c>
       <c r="H26" s="63"/>
       <c r="I26" s="63"/>
       <c r="J26" s="63"/>
@@ -11021,7 +11061,7 @@
       <c r="AI26" s="63"/>
       <c r="AJ26" s="36">
         <f t="shared" si="0"/>
-        <v>19.3</v>
+        <v>18.5</v>
       </c>
       <c r="AK26" s="21">
         <f t="shared" si="1"/>
@@ -11066,7 +11106,9 @@
       <c r="F27" s="63">
         <v>19.600000000000001</v>
       </c>
-      <c r="G27" s="63"/>
+      <c r="G27" s="63">
+        <v>19.2</v>
+      </c>
       <c r="H27" s="63"/>
       <c r="I27" s="63"/>
       <c r="J27" s="63"/>
@@ -11097,7 +11139,7 @@
       <c r="AI27" s="63"/>
       <c r="AJ27" s="36">
         <f t="shared" si="0"/>
-        <v>19.600000000000001</v>
+        <v>19.2</v>
       </c>
       <c r="AK27" s="21">
         <f t="shared" si="1"/>
@@ -11142,7 +11184,9 @@
       <c r="F28" s="63">
         <v>33.5</v>
       </c>
-      <c r="G28" s="63"/>
+      <c r="G28" s="63">
+        <v>31.7</v>
+      </c>
       <c r="H28" s="63"/>
       <c r="I28" s="63"/>
       <c r="J28" s="63"/>
@@ -11173,7 +11217,7 @@
       <c r="AI28" s="63"/>
       <c r="AJ28" s="36">
         <f t="shared" si="0"/>
-        <v>33.5</v>
+        <v>31.7</v>
       </c>
       <c r="AK28" s="21">
         <f t="shared" si="1"/>
@@ -11282,7 +11326,9 @@
       <c r="F30" s="63">
         <v>36.200000000000003</v>
       </c>
-      <c r="G30" s="63"/>
+      <c r="G30" s="63">
+        <v>36.200000000000003</v>
+      </c>
       <c r="H30" s="63"/>
       <c r="I30" s="63"/>
       <c r="J30" s="63"/>
@@ -11358,7 +11404,9 @@
       <c r="F31" s="63">
         <v>28</v>
       </c>
-      <c r="G31" s="63"/>
+      <c r="G31" s="63">
+        <v>28.2</v>
+      </c>
       <c r="H31" s="63"/>
       <c r="I31" s="63"/>
       <c r="J31" s="63"/>
@@ -11389,7 +11437,7 @@
       <c r="AI31" s="63"/>
       <c r="AJ31" s="36">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>28.2</v>
       </c>
       <c r="AK31" s="21">
         <f t="shared" si="1"/>
@@ -11434,7 +11482,9 @@
       <c r="F32" s="63">
         <v>17.600000000000001</v>
       </c>
-      <c r="G32" s="63"/>
+      <c r="G32" s="63">
+        <v>16.2</v>
+      </c>
       <c r="H32" s="63"/>
       <c r="I32" s="63"/>
       <c r="J32" s="63"/>
@@ -11465,7 +11515,7 @@
       <c r="AI32" s="63"/>
       <c r="AJ32" s="36">
         <f t="shared" si="0"/>
-        <v>17.600000000000001</v>
+        <v>16.2</v>
       </c>
       <c r="AK32" s="21">
         <f t="shared" si="1"/>
@@ -11510,7 +11560,9 @@
       <c r="F33" s="63">
         <v>16.2</v>
       </c>
-      <c r="G33" s="63"/>
+      <c r="G33" s="63">
+        <v>16.2</v>
+      </c>
       <c r="H33" s="63"/>
       <c r="I33" s="63"/>
       <c r="J33" s="63"/>
@@ -11638,7 +11690,9 @@
       <c r="F35" s="63">
         <v>32.799999999999997</v>
       </c>
-      <c r="G35" s="63"/>
+      <c r="G35" s="63">
+        <v>32.4</v>
+      </c>
       <c r="H35" s="63"/>
       <c r="I35" s="63"/>
       <c r="J35" s="63"/>
@@ -11669,7 +11723,7 @@
       <c r="AI35" s="63"/>
       <c r="AJ35" s="36">
         <f t="shared" si="0"/>
-        <v>32.799999999999997</v>
+        <v>32.4</v>
       </c>
       <c r="AK35" s="21">
         <f t="shared" si="1"/>
@@ -11833,7 +11887,9 @@
       <c r="F38" s="63">
         <v>30.3</v>
       </c>
-      <c r="G38" s="63"/>
+      <c r="G38" s="63">
+        <v>33.299999999999997</v>
+      </c>
       <c r="H38" s="63"/>
       <c r="I38" s="63"/>
       <c r="J38" s="63"/>
@@ -11864,7 +11920,7 @@
       <c r="AI38" s="63"/>
       <c r="AJ38" s="36">
         <f t="shared" si="0"/>
-        <v>30.3</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="AK38" s="21">
         <f t="shared" si="1"/>
@@ -11910,7 +11966,9 @@
       <c r="F39" s="63">
         <v>32.5</v>
       </c>
-      <c r="G39" s="63"/>
+      <c r="G39" s="63">
+        <v>33</v>
+      </c>
       <c r="H39" s="63"/>
       <c r="I39" s="63"/>
       <c r="J39" s="63"/>
@@ -11941,7 +11999,7 @@
       <c r="AI39" s="63"/>
       <c r="AJ39" s="36">
         <f t="shared" si="0"/>
-        <v>32.5</v>
+        <v>33</v>
       </c>
       <c r="AK39" s="21">
         <f t="shared" si="1"/>
@@ -11987,7 +12045,9 @@
       <c r="F40" s="63">
         <v>32</v>
       </c>
-      <c r="G40" s="63"/>
+      <c r="G40" s="63">
+        <v>33.200000000000003</v>
+      </c>
       <c r="H40" s="63"/>
       <c r="I40" s="63"/>
       <c r="J40" s="63"/>
@@ -12018,18 +12078,18 @@
       <c r="AI40" s="63"/>
       <c r="AJ40" s="36">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="AK40" s="21">
         <f t="shared" si="1"/>
-        <v>32</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="AL40" s="22">
         <v>35</v>
       </c>
       <c r="AM40" s="23">
         <f t="shared" si="2"/>
-        <v>-3</v>
+        <v>-1.7999999999999972</v>
       </c>
       <c r="AN40" s="23">
         <v>30.79898193760263</v>
@@ -12064,7 +12124,9 @@
       <c r="F41" s="63">
         <v>32.4</v>
       </c>
-      <c r="G41" s="63"/>
+      <c r="G41" s="63">
+        <v>33.200000000000003</v>
+      </c>
       <c r="H41" s="63"/>
       <c r="I41" s="63"/>
       <c r="J41" s="63"/>
@@ -12095,18 +12157,18 @@
       <c r="AI41" s="63"/>
       <c r="AJ41" s="36">
         <f t="shared" si="0"/>
-        <v>32.4</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="AK41" s="21">
         <f t="shared" si="1"/>
-        <v>32.4</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="AL41" s="22">
         <v>35</v>
       </c>
       <c r="AM41" s="23">
         <f t="shared" si="2"/>
-        <v>-2.6000000000000014</v>
+        <v>-1.7999999999999972</v>
       </c>
       <c r="AN41" s="23">
         <v>30.61551559934319</v>
@@ -12209,7 +12271,9 @@
       <c r="F43" s="63">
         <v>33.799999999999997</v>
       </c>
-      <c r="G43" s="63"/>
+      <c r="G43" s="63">
+        <v>33</v>
+      </c>
       <c r="H43" s="63"/>
       <c r="I43" s="63"/>
       <c r="J43" s="63"/>
@@ -12240,7 +12304,7 @@
       <c r="AI43" s="63"/>
       <c r="AJ43" s="36">
         <f t="shared" si="0"/>
-        <v>33.799999999999997</v>
+        <v>33</v>
       </c>
       <c r="AK43" s="21">
         <f t="shared" si="1"/>
@@ -12286,7 +12350,9 @@
       <c r="F44" s="29">
         <v>32</v>
       </c>
-      <c r="G44" s="29"/>
+      <c r="G44" s="29">
+        <v>31</v>
+      </c>
       <c r="H44" s="29"/>
       <c r="I44" s="29"/>
       <c r="J44" s="29"/>
@@ -12317,7 +12383,7 @@
       <c r="AI44" s="63"/>
       <c r="AJ44" s="36">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AK44" s="21">
         <f t="shared" si="1"/>
@@ -12363,7 +12429,9 @@
       <c r="F45" s="63">
         <v>33.200000000000003</v>
       </c>
-      <c r="G45" s="63"/>
+      <c r="G45" s="63">
+        <v>32.799999999999997</v>
+      </c>
       <c r="H45" s="63"/>
       <c r="I45" s="63"/>
       <c r="J45" s="63"/>
@@ -12394,7 +12462,7 @@
       <c r="AI45" s="63"/>
       <c r="AJ45" s="36">
         <f t="shared" si="0"/>
-        <v>33.200000000000003</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="AK45" s="21">
         <f t="shared" si="1"/>
@@ -12572,7 +12640,9 @@
       <c r="F48" s="63">
         <v>34.6</v>
       </c>
-      <c r="G48" s="63"/>
+      <c r="G48" s="63">
+        <v>32.6</v>
+      </c>
       <c r="H48" s="63"/>
       <c r="I48" s="63"/>
       <c r="J48" s="63"/>
@@ -12603,7 +12673,7 @@
       <c r="AI48" s="63"/>
       <c r="AJ48" s="36">
         <f t="shared" si="0"/>
-        <v>34.6</v>
+        <v>32.6</v>
       </c>
       <c r="AK48" s="21">
         <f t="shared" si="1"/>
@@ -25669,12 +25739,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
     <mergeCell ref="M1:M2"/>
     <mergeCell ref="N1:N2"/>
     <mergeCell ref="O1:O2"/>
@@ -25684,6 +25748,12 @@
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="L1:L2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:O13 D15:O31 D33:O34 D36:O46">
     <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="equal">
